--- a/Representantes tecnicos .xlsx
+++ b/Representantes tecnicos .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicholaspalmacarvajal/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72CC544D-75A4-774B-B6EE-B09B01F7CD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E519DF-AB44-A34D-8D7A-ED6962E0021B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{5F8E7E6C-D5D5-7844-B7A6-F22034E12E8E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>carlos.narbona@rentokil-initial.com</t>
+  </si>
+  <si>
+    <t>CURICO</t>
   </si>
 </sst>
 </file>
@@ -611,13 +614,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>7</v>
@@ -625,16 +628,16 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
